--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.6483</v>
+        <v>17.09331</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59426</v>
+        <v>16.66349</v>
       </c>
       <c r="E2" t="n">
-        <v>16.86583</v>
+        <v>16.82149</v>
       </c>
       <c r="F2" t="n">
-        <v>41.96828</v>
+        <v>42.70942</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05079</v>
+        <v>0.05037</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83815</v>
+        <v>1.81598</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.65277</v>
+        <v>16.5691</v>
       </c>
       <c r="D3" t="n">
-        <v>16.54476</v>
+        <v>16.43855</v>
       </c>
       <c r="E3" t="n">
-        <v>16.80815</v>
+        <v>16.54876</v>
       </c>
       <c r="F3" t="n">
-        <v>42.25237</v>
+        <v>42.06019</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05095</v>
+        <v>0.05051</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81709</v>
+        <v>1.80729</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.72731</v>
+        <v>16.5976</v>
       </c>
       <c r="D4" t="n">
-        <v>16.58936</v>
+        <v>16.36723</v>
       </c>
       <c r="E4" t="n">
-        <v>16.36285</v>
+        <v>16.38074</v>
       </c>
       <c r="F4" t="n">
-        <v>43.48149</v>
+        <v>41.19479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05026</v>
+        <v>0.05036</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79044</v>
+        <v>1.81267</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8618</v>
+        <v>16.44709</v>
       </c>
       <c r="D6" t="n">
-        <v>16.02915</v>
+        <v>15.97894</v>
       </c>
       <c r="E6" t="n">
-        <v>16.16443</v>
+        <v>16.427</v>
       </c>
       <c r="F6" t="n">
-        <v>21.98547</v>
+        <v>21.5934</v>
       </c>
       <c r="G6" t="n">
-        <v>34.10556</v>
+        <v>33.98966</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.07318</v>
+        <v>16.7375</v>
       </c>
       <c r="D7" t="n">
-        <v>16.06061</v>
+        <v>15.9291</v>
       </c>
       <c r="E7" t="n">
-        <v>16.47098</v>
+        <v>16.3759</v>
       </c>
       <c r="F7" t="n">
-        <v>22.27224</v>
+        <v>21.86172</v>
       </c>
       <c r="G7" t="n">
-        <v>34.29615</v>
+        <v>34.6569</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.95049</v>
+        <v>16.641</v>
       </c>
       <c r="D8" t="n">
-        <v>16.20297</v>
+        <v>16.21673</v>
       </c>
       <c r="E8" t="n">
-        <v>16.50009</v>
+        <v>16.45819</v>
       </c>
       <c r="F8" t="n">
-        <v>21.70715</v>
+        <v>21.90484</v>
       </c>
       <c r="G8" t="n">
-        <v>33.4762</v>
+        <v>33.75382</v>
       </c>
     </row>
   </sheetData>
